--- a/docs/功能清单-进度跟踪.xlsx
+++ b/docs/功能清单-进度跟踪.xlsx
@@ -11593,7 +11593,7 @@
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>底座裁剪 + 工程化（CI/docker-compose/规范）</t>
+          <t>底座裁剪 + 私有仓库与工程化（CI/docker-compose/规范）</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr"/>
@@ -11631,7 +11631,7 @@
       <c r="M182" s="5" t="inlineStr"/>
       <c r="N182" s="6" t="inlineStr">
         <is>
-          <t>含 license-maven-plugin + license-checker 进 CI</t>
+          <t>GitHub 私有仓库建立+双远程（origin/upstream）+main 分支保护；含 license-maven-plugin + license-checker 进 CI；对应计划 §5.1 任务 4 / §8.2</t>
         </is>
       </c>
     </row>

--- a/docs/功能清单-进度跟踪.xlsx
+++ b/docs/功能清单-进度跟踪.xlsx
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -687,62 +687,66 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>完成时间：填实际完成/验收日期 YYYY-MM-DD；这是记录字段，不是排期字段（排期看阶段列+计划 §9）</t>
+          <t>状态（前置条件）：功能标「已完成」的前提 = 单测+冒烟自检通过 且 已 commit+push 且 CI 绿；测试不过、未推送的不得标已完成</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>完成时间：填实际完成/验收日期 YYYY-MM-DD（完成 = 测试通过+已推送）；这是记录字段，不是排期字段（排期看阶段列+计划 §5）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>【维护规则】</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>1. 每周例会过一遍『进行中』项；里程碑结束批量对账</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2. 状态只能前进：返工不改回状态，在备注记『YYYY-MM-DD 返工：原因』</t>
+          <t>1. 每周例会过一遍『进行中』项；里程碑结束批量对账</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>3. 新增功能追加行（ID 顺延）不删历史；砍掉的功能标『已取消』+备注</t>
+          <t>2. 状态只能前进：返工不改回状态，在备注记『YYYY-MM-DD 返工：原因』</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>3. 新增功能追加行（ID 顺延）不删历史；砍掉的功能标『已取消』+备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>4. 优先级变更需例会确认并同步计划文档 §2，备注记录原因（已发生：广告图/轮播图 P0、同城配送 P0、隐私政策 P0）</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-    </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>【ID 规则】A-xx 后台管理端 · C-xx 顾客端 · M-xx 商家中心 · R-xx 骑手中心 · S-xx 门店端 · X-xx 横切技术项</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>5. 及时测试：功能开发完成立即测试（单测+冒烟），测试不过不改状态、不提交；禁止积压到里程碑末尾</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>ID 锚定原文件行序（后台 A-01~98 = 原行2-99；顾客 C-03~49 = 原行101-159；商家 M-01~06 = 原行144-149；骑手 R-01~06 = 原行150-155；门店 S-01~19 = 原行160-178）；编号永不复用</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>6. 及时推送：每次 commit 后立即 push 到 origin 并确认 CI 绿（红灯当天修复）；工作区不留未推送代码</t>
         </is>
       </c>
     </row>
@@ -752,14 +756,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>【P0 上线门槛】A/C/S 端全部 P0 项达『已验收』+ M2/M3/M4-P0 里程碑验收通过（计划 §5.0）</t>
+          <t>【ID 规则】A-xx 后台管理端 · C-xx 顾客端 · M-xx 商家中心 · R-xx 骑手中心 · S-xx 门店端 · X-xx 横切技术项</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>【核心域必过单测】X-05 支付幂等 / X-12 优惠管道 / X-13 协同域 / X-08 提现域（计划 §8）</t>
+          <t>ID 锚定原文件行序（后台 A-01~98 = 原行2-99；顾客 C-03~49 = 原行101-159；商家 M-01~06 = 原行144-149；骑手 R-01~06 = 原行150-155；门店 S-01~19 = 原行160-178）；编号永不复用</t>
         </is>
       </c>
     </row>
@@ -768,6 +772,23 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>【P0 上线门槛】A/C/S 端全部 P0 项达『已验收』+ M2/M3/M4-P0 里程碑验收通过（计划 §5.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>【核心域必过单测】X-05 支付幂等 / X-12 优惠管道 / X-13 协同域 / X-08 提现域（计划 §8）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>【颜色约定】重要性列：红=P0 黄=P1 绿=P2；状态列：蓝=进行中 绿=已完成/已验收 灰=已取消（删除线）</t>
         </is>

--- a/docs/功能清单-进度跟踪.xlsx
+++ b/docs/功能清单-进度跟踪.xlsx
@@ -569,7 +569,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>功能清单与进度跟踪（v1.1 · 2026-09-05）</t>
+          <t>功能清单与进度跟踪（2026-09-05）</t>
         </is>
       </c>
     </row>
@@ -12304,6 +12304,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -12377,6 +12378,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
@@ -12450,6 +12452,7 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
@@ -12490,6 +12493,7 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -12519,6 +12523,7 @@
         <v/>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>

--- a/docs/功能清单-进度跟踪.xlsx
+++ b/docs/功能清单-进度跟踪.xlsx
@@ -780,7 +780,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>【核心域必过单测】X-05 支付幂等 / X-12 优惠管道 / X-13 协同域 / X-08 提现域（计划 §8）</t>
+          <t>【核心域必过单测】X-05 支付幂等 / X-12 优惠管道 / X-13 协同域 / X-08 提现域（AI-工程手册）</t>
         </is>
       </c>
     </row>
@@ -12304,7 +12304,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -12378,7 +12377,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
@@ -12452,7 +12450,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
@@ -12493,7 +12490,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -12523,7 +12519,6 @@
         <v/>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>

--- a/docs/功能清单-进度跟踪.xlsx
+++ b/docs/功能清单-进度跟踪.xlsx
@@ -583,7 +583,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>本文件是功能的唯一事实源（做没做/怎么做/谁在做/何时完成）；配套《点餐SaaS-详细实施计划.md》《开源授权核验报告.md》</t>
+          <t>本文件是功能的唯一事实源（做没做/怎么做/谁在做/何时完成）；配套《点餐SaaS-详细实施计划.md》《派单指南.md》《AI-工程手册.md》《开源授权核验报告.md》</t>
         </is>
       </c>
     </row>
